--- a/app/Archivos/Remittance/Remittance_copi.xlsx
+++ b/app/Archivos/Remittance/Remittance_copi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unilever-my.sharepoint.com/personal/jose-ricardo_morales_unilever_com/Documents/Cartera/PROYECTOS/Cash App Cross Andina/Python/Unilever_Collect_Digital/app/Archivos/Remittance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{44AC9C51-96AC-4375-9CE1-1101779D2EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EC1DF5E-37A3-46F4-99D8-8CEBA50712C5}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{44AC9C51-96AC-4375-9CE1-1101779D2EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AAF0AC1-9468-44A0-B3AF-97BCE8AAFD89}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A4FF0199-2636-4D5A-A5AA-72A4E1DC7BA9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="82">
   <si>
     <t>Facturas Pagadas
 Proveedor: UNILEVER ANDINA COLOMBIA LTDA
@@ -106,169 +106,187 @@
     <t>UNILEVER ANDINA COLOMBIA LTDA/CONCILIACION</t>
   </si>
   <si>
-    <t>Ventas</t>
-  </si>
-  <si>
     <t>Factura Acrededor</t>
   </si>
   <si>
-    <t>Cartera</t>
-  </si>
-  <si>
-    <t>Barranquilla</t>
-  </si>
-  <si>
-    <t>13/08/2025</t>
-  </si>
-  <si>
     <t>Palmira</t>
   </si>
   <si>
-    <t>12/08/2025</t>
-  </si>
-  <si>
     <t>Cota</t>
   </si>
   <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
     <t>Cerritos</t>
   </si>
   <si>
-    <t>08/09/2025</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>PMP1276670</t>
-  </si>
-  <si>
-    <t>12/09/2025</t>
-  </si>
-  <si>
-    <t>20/08/2025</t>
-  </si>
-  <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>PMP1276992</t>
-  </si>
-  <si>
-    <t>21/08/2025</t>
-  </si>
-  <si>
-    <t>UNILEVER ANDINA COLOMBIA LTDA/conciliaicon</t>
-  </si>
-  <si>
-    <t>PMP1277139</t>
-  </si>
-  <si>
     <t>Devolucion</t>
   </si>
   <si>
-    <t>AVERIAS</t>
-  </si>
-  <si>
     <t>C. UNILEVER</t>
   </si>
   <si>
     <t>DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</t>
   </si>
   <si>
-    <t>DPP</t>
-  </si>
-  <si>
-    <t>NOTA DEVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
-  </si>
-  <si>
-    <t>AUT.G.COMERCIAL</t>
-  </si>
-  <si>
-    <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL </t>
-  </si>
-  <si>
-    <t>10/09/2025</t>
-  </si>
-  <si>
-    <t>DDPD UNILEVER MIN 2Q 2025</t>
-  </si>
-  <si>
-    <t>PMP1276671</t>
-  </si>
-  <si>
-    <t>PMP1277137</t>
-  </si>
-  <si>
-    <t>UNILEVER ANDINA COLOMBIA LTDA/conciliacion</t>
-  </si>
-  <si>
-    <t>PMP1276991</t>
-  </si>
-  <si>
-    <t>UNILEVER ANDINA COLOMBIA LTDA/CONCILIAICION</t>
-  </si>
-  <si>
-    <t>PMP-1273112</t>
-  </si>
-  <si>
-    <t>PMP1273596</t>
-  </si>
-  <si>
-    <t>PMP1273112</t>
-  </si>
-  <si>
-    <t>PMP1273863</t>
-  </si>
-  <si>
-    <t>PMP1273878</t>
-  </si>
-  <si>
-    <t>PMP1276669</t>
-  </si>
-  <si>
-    <t>PMP1277138</t>
-  </si>
-  <si>
-    <t>PMP1276993</t>
-  </si>
-  <si>
-    <t>PMP1276666</t>
-  </si>
-  <si>
-    <t>PMP1276672</t>
-  </si>
-  <si>
-    <t>PMP1276673</t>
-  </si>
-  <si>
-    <t>PMP1276668</t>
-  </si>
-  <si>
-    <t>PMP1277145</t>
-  </si>
-  <si>
-    <t>PMP1277144</t>
-  </si>
-  <si>
-    <t>PMP1276990</t>
-  </si>
-  <si>
-    <t>PMP1277143</t>
-  </si>
-  <si>
-    <t>PMP1277142</t>
-  </si>
-  <si>
-    <t>PMP1276988</t>
+    <t>PMP1280801</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>PMP1280799</t>
+  </si>
+  <si>
+    <t>PMP1280671</t>
+  </si>
+  <si>
+    <t>PMP1281555</t>
+  </si>
+  <si>
+    <t>30/08/2025</t>
+  </si>
+  <si>
+    <t>PMP1280493</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>UNILEVER ANDINA COLOMBIA LTDA // CONCILIACIÓN</t>
+  </si>
+  <si>
+    <t>PMP1281903</t>
+  </si>
+  <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>PDI PRODUCTO DEL DÍA 08 Y 09 SEP 2025 UNILEVER</t>
+  </si>
+  <si>
+    <t>FARMAEXPRESS</t>
+  </si>
+  <si>
+    <t>ACTIVIDAD FARMAEXPRESS AGOSTO</t>
+  </si>
+  <si>
+    <t>PMP1281554</t>
+  </si>
+  <si>
+    <t>PMP1281913</t>
+  </si>
+  <si>
+    <t>PMP1281556</t>
+  </si>
+  <si>
+    <t>PMP1281902</t>
+  </si>
+  <si>
+    <t>PMP1280496</t>
+  </si>
+  <si>
+    <t>31/08/2025</t>
+  </si>
+  <si>
+    <t>PMP1280494</t>
+  </si>
+  <si>
+    <t>PMP1280498</t>
+  </si>
+  <si>
+    <t>PMP1280672</t>
+  </si>
+  <si>
+    <t>PMP1280674</t>
+  </si>
+  <si>
+    <t>PMP1281560</t>
+  </si>
+  <si>
+    <t>PMP1280803</t>
+  </si>
+  <si>
+    <t>PMP1281553</t>
+  </si>
+  <si>
+    <t>PMP1280500</t>
+  </si>
+  <si>
+    <t>PMP1281907</t>
+  </si>
+  <si>
+    <t>PMP1281906</t>
+  </si>
+  <si>
+    <t>PMP1281559</t>
+  </si>
+  <si>
+    <t>PMP1280805</t>
+  </si>
+  <si>
+    <t>PMP1280804</t>
+  </si>
+  <si>
+    <t>PMP´1280804</t>
+  </si>
+  <si>
+    <t>PMP1281911</t>
+  </si>
+  <si>
+    <t>PMP1281905</t>
+  </si>
+  <si>
+    <t>PMP1281910</t>
+  </si>
+  <si>
+    <t>PMP1281563</t>
+  </si>
+  <si>
+    <t>PMP1281557</t>
+  </si>
+  <si>
+    <t>PMP1280675</t>
+  </si>
+  <si>
+    <t>PMP1281561</t>
+  </si>
+  <si>
+    <t>PMP1280495</t>
+  </si>
+  <si>
+    <t>PMP1280497</t>
+  </si>
+  <si>
+    <t>PMP1280499</t>
+  </si>
+  <si>
+    <t>PMP1280492</t>
+  </si>
+  <si>
+    <t>17/09/2025</t>
+  </si>
+  <si>
+    <t>0107740435</t>
+  </si>
+  <si>
+    <t>Traslado proximo Pago proveedor</t>
+  </si>
+  <si>
+    <t>0107744770</t>
+  </si>
+  <si>
+    <t>Traslado Notas  Deudor acreedor</t>
   </si>
 </sst>
 </file>
@@ -712,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA5F87B-7EBD-4E78-9BF0-7A754A9939D9}">
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -800,7 +818,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -812,40 +830,35 @@
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
-        <v>5100335942</v>
+        <v>5100347193</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>4956</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="6" t="str">
-        <f>+H3&amp;" "&amp;E3</f>
-        <v>Reduc Factura Compra PMP1276670</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>-1674084</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>16</v>
@@ -857,40 +870,35 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1">
-        <v>5100335941</v>
+        <v>5100347220</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>-8387269</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" s="6" t="str">
-        <f>+H4&amp;" "&amp; E4</f>
-        <v>Factura Acrededor PMP1276670</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>-478309</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -902,40 +910,38 @@
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
-        <v>5100337112</v>
+        <v>5100346829</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>4956</v>
+        <v>-392620</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="6" t="str">
-        <f>+H5&amp;" "&amp;E5</f>
-        <v>Reduc Factura Compra PMP1276992</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
@@ -947,43 +953,35 @@
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>5100337864</v>
+        <v>5100348603</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>-20008459</v>
+        <v>1384596</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" s="6" t="str">
-        <f t="shared" ref="N6:N7" si="0">+H6&amp;" "&amp; E6</f>
-        <v>Factura Acrededor PMP1277139</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>16</v>
@@ -995,40 +993,35 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>5100337111</v>
+        <v>5100348602</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>-19850219</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>Factura Acrededor PMP1276992</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>-65289584</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
@@ -1040,40 +1033,38 @@
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>1700028193</v>
+        <v>5100346838</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>15664649</v>
+        <v>1803455</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N8" s="6" t="str">
-        <f t="shared" ref="N8:N12" si="1">+M8</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>16</v>
@@ -1085,43 +1076,38 @@
         <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
-        <v>1700028002</v>
+        <v>5100346837</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>23148793</v>
+        <v>-154830920</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>16</v>
@@ -1133,43 +1119,38 @@
         <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1">
-        <v>1700027852</v>
+        <v>5100348419</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>136694904</v>
+        <v>-28939375</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>16</v>
@@ -1181,43 +1162,38 @@
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G11" s="1">
-        <v>1700027696</v>
+        <v>5100348420</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>58852874</v>
+        <v>261536</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>16</v>
@@ -1228,44 +1204,36 @@
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>46</v>
+      <c r="E12" s="1">
+        <v>5009127650</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>1700027502</v>
+        <v>5100363388</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>25771569</v>
+        <v>41859</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -1276,44 +1244,37 @@
       <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>48</v>
+      <c r="E13" s="1">
+        <v>5009127719</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G13" s="1">
-        <v>1700028339</v>
+        <v>5100363413</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>110942</v>
+        <v>103883</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="6" t="str">
-        <f t="shared" ref="N13" si="2">+M13</f>
-        <v>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>16</v>
@@ -1324,41 +1285,36 @@
       <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E14" s="1">
+        <v>5009128765</v>
+      </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
-        <v>1700028683</v>
+        <v>5100363860</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14" s="5">
-        <v>82067413</v>
+        <v>91263</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14" s="6" t="str">
-        <f>+M14</f>
-        <v>DDPD UNILEVER MIN 2Q 2025</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -1369,41 +1325,36 @@
       <c r="D15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>43</v>
+      <c r="E15" s="1">
+        <v>5009131816</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1">
-        <v>1700028726</v>
+        <v>5100364342</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>22013501</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N15" s="6" t="str">
-        <f t="shared" ref="N15" si="3">+M15</f>
-        <v>DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>45</v>
-      </c>
+        <v>124580</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>605</v>
+        <v>368</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
@@ -1414,41 +1365,36 @@
       <c r="D16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
-        <v>5100335935</v>
+        <v>1700029164</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>-23118825</v>
+        <v>174370398</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" s="6" t="str">
-        <f>+H16&amp;" "&amp; E16</f>
-        <v>Factura Acrededor PMP1276671</v>
-      </c>
-      <c r="O16" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="M16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>606</v>
+        <v>369</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
@@ -1459,41 +1405,36 @@
       <c r="D17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>53</v>
+      <c r="E17" s="1">
+        <v>5009146321</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
-        <v>5100335936</v>
+        <v>5100367951</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>128471</v>
+        <v>34628</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="6" t="str">
-        <f>+H17&amp;" "&amp;E17</f>
-        <v>Reduc Factura Compra PMP1276671</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>609</v>
+        <v>370</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
@@ -1504,44 +1445,36 @@
       <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>54</v>
+      <c r="E18" s="1">
+        <v>5009142447</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G18" s="1">
-        <v>5100337263</v>
+        <v>5100367092</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
       </c>
       <c r="K18" s="5">
-        <v>973783</v>
+        <v>84105</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" s="6" t="str">
-        <f>+H18&amp;" "&amp;E18</f>
-        <v>Reduc Factura Compra PMP1277137</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>610</v>
+        <v>372</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -1553,40 +1486,38 @@
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G19" s="1">
-        <v>5100337491</v>
+        <v>1700029194</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>-21513304</v>
+        <v>142051</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N19" s="6" t="str">
-        <f t="shared" ref="N19:N20" si="4">+H19&amp;" "&amp; E19</f>
-        <v>Factura Acrededor PMP1276991</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>611</v>
+        <v>373</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>16</v>
@@ -1598,43 +1529,35 @@
         <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1">
-        <v>5100337262</v>
+        <v>1700029213</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="5">
-        <v>-111539485</v>
-      </c>
-      <c r="L20" s="1" t="s">
+        <v>18424430</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N20" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v>Factura Acrededor PMP1277137</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>16</v>
@@ -1646,40 +1569,35 @@
         <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1">
-        <v>5100337492</v>
+        <v>5100348634</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J21" s="1">
         <v>0</v>
       </c>
       <c r="K21" s="5">
-        <v>375295</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N21" s="6" t="str">
-        <f t="shared" ref="N21" si="5">+H21&amp;" "&amp;E21</f>
-        <v>Reduc Factura Compra PMP1276991</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>148362</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
@@ -1691,40 +1609,38 @@
         <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1">
-        <v>1700028194</v>
+        <v>5100347522</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>28813</v>
+        <v>-142499</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="6" t="str">
-        <f t="shared" ref="N22" si="6">+M22</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -1739,40 +1655,32 @@
         <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G23" s="1">
-        <v>1700027503</v>
+        <v>5100348633</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J23" s="1">
         <v>0</v>
       </c>
       <c r="K23" s="5">
-        <v>3659996</v>
+        <v>-44361726</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N23" s="6" t="str">
-        <f t="shared" ref="N23:N25" si="7">+M23</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>639</v>
+        <v>619</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>16</v>
@@ -1784,43 +1692,35 @@
         <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G24" s="1">
-        <v>1700027697</v>
+        <v>5100346893</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J24" s="1">
         <v>0</v>
       </c>
       <c r="K24" s="5">
-        <v>1074320</v>
+        <v>-445336</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N24" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>16</v>
@@ -1832,43 +1732,38 @@
         <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G25" s="1">
-        <v>1700027853</v>
+        <v>5100347521</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J25" s="1">
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>8010033</v>
+        <v>11127</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N25" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O25" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>16</v>
@@ -1880,43 +1775,38 @@
         <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G26" s="1">
-        <v>1700028003</v>
+        <v>5100347520</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J26" s="1">
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>209929</v>
+        <v>-2880476</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N26" s="6" t="str">
-        <f>+M26</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>16</v>
@@ -1928,43 +1818,38 @@
         <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1">
-        <v>1700028340</v>
+        <v>5100346707</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="J27" s="1">
         <v>0</v>
       </c>
       <c r="K27" s="5">
-        <v>97776</v>
+        <v>-1203485</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N27" s="6" t="str">
-        <f>+M27</f>
-        <v>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</v>
-      </c>
-      <c r="O27" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>950</v>
+        <v>626</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>16</v>
@@ -1976,40 +1861,38 @@
         <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G28" s="1">
-        <v>5100315882</v>
+        <v>5100346728</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J28" s="1">
         <v>0</v>
       </c>
       <c r="K28" s="5">
-        <v>-27974992</v>
+        <v>-26667920</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="6" t="str">
-        <f t="shared" ref="N28:N29" si="8">+H28&amp;" "&amp; E28</f>
-        <v>Factura Acrededor PMP-1273112</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>951</v>
+        <v>627</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>16</v>
@@ -2021,43 +1904,38 @@
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G29" s="1">
-        <v>5100317247</v>
+        <v>5100346729</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
       </c>
       <c r="K29" s="5">
-        <v>-28749643</v>
+        <v>66594</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>Factura Acrededor PMP1273596</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>952</v>
+        <v>660</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>16</v>
@@ -2068,41 +1946,36 @@
       <c r="D30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>60</v>
+      <c r="E30" s="1">
+        <v>5009127691</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G30" s="1">
-        <v>5100315883</v>
+        <v>5100363389</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J30" s="1">
         <v>0</v>
       </c>
       <c r="K30" s="5">
-        <v>98733</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N30" s="6" t="str">
-        <f>+H30&amp;" "&amp;E30</f>
-        <v>Reduc Factura Compra PMP1273112</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>66728</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>954</v>
+        <v>663</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>16</v>
@@ -2113,41 +1986,36 @@
       <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>61</v>
+      <c r="E31" s="1">
+        <v>5009134505</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G31" s="1">
-        <v>5100318608</v>
+        <v>5100364980</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J31" s="1">
         <v>0</v>
       </c>
       <c r="K31" s="5">
-        <v>-11408205</v>
+        <v>15428</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N31" s="6" t="str">
-        <f>+H31&amp;" "&amp; E31</f>
-        <v>Factura Acrededor PMP1273863</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>955</v>
+        <v>664</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>16</v>
@@ -2158,44 +2026,36 @@
       <c r="D32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>62</v>
+      <c r="E32" s="1">
+        <v>5009131760</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G32" s="1">
-        <v>5100318343</v>
+        <v>5100364337</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J32" s="1">
         <v>0</v>
       </c>
       <c r="K32" s="5">
-        <v>1267188</v>
+        <v>164766</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N32" s="6" t="str">
-        <f>+H32&amp;" "&amp;E32</f>
-        <v>Reduc Factura Compra PMP1273878</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>956</v>
+        <v>665</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>16</v>
@@ -2206,44 +2066,36 @@
       <c r="D33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>62</v>
+      <c r="E33" s="1">
+        <v>5009128766</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1">
-        <v>5100318342</v>
+        <v>5100363861</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J33" s="1">
         <v>0</v>
       </c>
       <c r="K33" s="5">
-        <v>-154734955</v>
+        <v>26879</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N33" s="6" t="str">
-        <f t="shared" ref="N33" si="9">+H33&amp;" "&amp; E33</f>
-        <v>Factura Acrededor PMP1273878</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>1005</v>
+        <v>666</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>16</v>
@@ -2255,40 +2107,35 @@
         <v>17</v>
       </c>
       <c r="E34" s="1">
-        <v>5009108214</v>
+        <v>5009142471</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1">
-        <v>5100358331</v>
+        <v>5100367094</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="J34" s="1">
         <v>0</v>
       </c>
       <c r="K34" s="5">
-        <v>2743</v>
+        <v>274228</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N34" s="6" t="str">
-        <f t="shared" ref="N34:N36" si="10">_xlfn.CONCAT(H34 &amp;" "&amp; E34)</f>
-        <v>Devolucion 5009108214</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>1006</v>
+        <v>1319</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>16</v>
@@ -2299,41 +2146,39 @@
       <c r="D35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="1">
-        <v>5009109080</v>
+      <c r="E35" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G35" s="1">
-        <v>5100358759</v>
+        <v>5100346818</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="J35" s="1">
         <v>0</v>
       </c>
       <c r="K35" s="5">
-        <v>13069</v>
+        <v>-56542409</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N35" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v>Devolucion 5009109080</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>1007</v>
+        <v>1320</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>16</v>
@@ -2344,41 +2189,39 @@
       <c r="D36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="1">
-        <v>5009114474</v>
+      <c r="E36" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G36" s="1">
-        <v>5100360110</v>
+        <v>5100346898</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
       </c>
       <c r="K36" s="5">
-        <v>5876</v>
+        <v>8946888</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N36" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v>Devolucion 5009114474</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>1303</v>
+        <v>1321</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>16</v>
@@ -2390,40 +2233,38 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G37" s="1">
-        <v>5100335924</v>
+        <v>5100346897</v>
       </c>
       <c r="H37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>-22367012</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5">
-        <v>-18919275</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N37" s="6" t="str">
-        <f t="shared" ref="N37:N39" si="11">+H37&amp;" "&amp; E37</f>
-        <v>Factura Acrededor PMP1276669</v>
-      </c>
-      <c r="O37" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="M37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>1305</v>
+        <v>1322</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>16</v>
@@ -2435,43 +2276,35 @@
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G38" s="1">
-        <v>5100337140</v>
+        <v>5100347187</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J38" s="1">
         <v>0</v>
       </c>
       <c r="K38" s="5">
-        <v>-25908600</v>
+        <v>-14409194</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N38" s="6" t="str">
-        <f t="shared" si="11"/>
-        <v>Factura Acrededor PMP1277138</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>1306</v>
+        <v>1323</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>16</v>
@@ -2483,40 +2316,35 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G39" s="1">
-        <v>5100337104</v>
+        <v>5100347205</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J39" s="1">
         <v>0</v>
       </c>
       <c r="K39" s="5">
-        <v>-24310076</v>
+        <v>-871442</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N39" s="6" t="str">
-        <f t="shared" si="11"/>
-        <v>Factura Acrededor PMP1276993</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>16</v>
@@ -2528,43 +2356,35 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1">
-        <v>1700027505</v>
+        <v>5100347206</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J40" s="1">
         <v>0</v>
       </c>
       <c r="K40" s="5">
-        <v>52023765</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>24</v>
+        <v>348580</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N40" s="6" t="str">
-        <f>+M40</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>1332</v>
+        <v>1325</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>16</v>
@@ -2576,43 +2396,35 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G41" s="1">
-        <v>1700027317</v>
+        <v>5100349876</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J41" s="1">
         <v>0</v>
       </c>
       <c r="K41" s="5">
-        <v>9458910</v>
+        <v>2950968</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" s="6" t="str">
-        <f>+M41</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>1335</v>
+        <v>1326</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>16</v>
@@ -2624,43 +2436,35 @@
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G42" s="1">
-        <v>1700027699</v>
+        <v>5100349875</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J42" s="1">
         <v>0</v>
       </c>
       <c r="K42" s="5">
-        <v>5923198</v>
+        <v>-175961573</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N42" s="6" t="str">
-        <f t="shared" ref="N42:N44" si="12">+M42</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>1336</v>
+        <v>1327</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>16</v>
@@ -2672,43 +2476,38 @@
         <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G43" s="1">
-        <v>1700028005</v>
+        <v>5100346720</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J43" s="1">
         <v>0</v>
       </c>
       <c r="K43" s="5">
-        <v>6652327</v>
+        <v>-15138774</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N43" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>16</v>
@@ -2720,40 +2519,38 @@
         <v>17</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G44" s="1">
-        <v>1700028196</v>
+        <v>5100347544</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J44" s="1">
         <v>0</v>
       </c>
       <c r="K44" s="5">
-        <v>14421092</v>
+        <v>-14226799</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N44" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>16</v>
@@ -2765,43 +2562,38 @@
         <v>17</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G45" s="1">
-        <v>1700028336</v>
+        <v>5100348511</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J45" s="1">
         <v>0</v>
       </c>
       <c r="K45" s="5">
-        <v>1059035</v>
+        <v>-101036650</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N45" s="6" t="str">
-        <f>+M45</f>
-        <v>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>1719</v>
+        <v>1343</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>16</v>
@@ -2813,16 +2605,16 @@
         <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G46" s="1">
-        <v>5100335919</v>
+        <v>5100348512</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>35</v>
@@ -2831,22 +2623,20 @@
         <v>0</v>
       </c>
       <c r="K46" s="5">
-        <v>-64246828</v>
+        <v>1195905</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N46" s="6" t="str">
-        <f>+H46&amp;" "&amp; E46</f>
-        <v>Factura Acrededor PMP1276666</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>1720</v>
+        <v>1380</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>16</v>
@@ -2857,41 +2647,36 @@
       <c r="D47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>66</v>
+      <c r="E47" s="1">
+        <v>5009127693</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G47" s="1">
-        <v>5100335920</v>
+        <v>5100363391</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J47" s="1">
         <v>0</v>
       </c>
       <c r="K47" s="5">
-        <v>116211</v>
+        <v>65576</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N47" s="6" t="str">
-        <f>+H47&amp;" "&amp;E47</f>
-        <v>Reduc Factura Compra PMP1276666</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>1721</v>
+        <v>1381</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>16</v>
@@ -2902,41 +2687,36 @@
       <c r="D48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>67</v>
+      <c r="E48" s="1">
+        <v>5009131968</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G48" s="1">
-        <v>5100335922</v>
+        <v>5100364376</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J48" s="1">
         <v>0</v>
       </c>
       <c r="K48" s="5">
-        <v>-223440</v>
+        <v>2160646</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N48" s="6" t="str">
-        <f t="shared" ref="N48:N50" si="13">+H48&amp;" "&amp; E48</f>
-        <v>Factura Acrededor PMP1276672</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>1722</v>
+        <v>1382</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>16</v>
@@ -2947,41 +2727,36 @@
       <c r="D49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>68</v>
+      <c r="E49" s="1">
+        <v>5009128769</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G49" s="1">
-        <v>5100335926</v>
+        <v>5100363865</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J49" s="1">
         <v>0</v>
       </c>
       <c r="K49" s="5">
-        <v>-2457840</v>
+        <v>214030</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N49" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v>Factura Acrededor PMP1276673</v>
-      </c>
-      <c r="O49" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>1723</v>
+        <v>1383</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>16</v>
@@ -2992,41 +2767,36 @@
       <c r="D50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>69</v>
+      <c r="E50" s="1">
+        <v>5009142423</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G50" s="1">
-        <v>5100335951</v>
+        <v>5100367082</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J50" s="1">
         <v>0</v>
       </c>
       <c r="K50" s="5">
-        <v>-65729254</v>
+        <v>279693</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N50" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v>Factura Acrededor PMP1276668</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>1724</v>
+        <v>1384</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>16</v>
@@ -3037,41 +2807,36 @@
       <c r="D51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>69</v>
+      <c r="E51" s="1">
+        <v>5009145996</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G51" s="1">
-        <v>5100335952</v>
+        <v>5100367867</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
       </c>
       <c r="K51" s="5">
-        <v>338713</v>
+        <v>171360</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N51" s="6" t="str">
-        <f>+H51&amp;" "&amp;E51</f>
-        <v>Reduc Factura Compra PMP1276668</v>
-      </c>
-      <c r="O51" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>1726</v>
+        <v>1385</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>16</v>
@@ -3082,44 +2847,36 @@
       <c r="D52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>70</v>
+      <c r="E52" s="1">
+        <v>5009146322</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G52" s="1">
-        <v>5100337144</v>
+        <v>5100367952</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J52" s="1">
         <v>0</v>
       </c>
       <c r="K52" s="5">
-        <v>-11842275</v>
+        <v>55774</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N52" s="6" t="str">
-        <f t="shared" ref="N52:N53" si="14">+H52&amp;" "&amp; E52</f>
-        <v>Factura Acrededor PMP1277145</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>1727</v>
+        <v>1762</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>16</v>
@@ -3131,43 +2888,35 @@
         <v>17</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G53" s="1">
-        <v>5100337147</v>
+        <v>5100346947</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
       </c>
       <c r="K53" s="5">
-        <v>-19509586</v>
+        <v>-13106355</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N53" s="6" t="str">
-        <f t="shared" si="14"/>
-        <v>Factura Acrededor PMP1277144</v>
-      </c>
-      <c r="O53" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>1728</v>
+        <v>1763</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>16</v>
@@ -3179,40 +2928,35 @@
         <v>17</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G54" s="1">
-        <v>5100337390</v>
+        <v>5100346948</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J54" s="1">
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <v>538091</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N54" s="6" t="str">
-        <f>+H54&amp;" "&amp;E54</f>
-        <v>Reduc Factura Compra PMP1276990</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>254441</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>1729</v>
+        <v>1764</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>16</v>
@@ -3224,40 +2968,35 @@
         <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G55" s="1">
-        <v>5100337389</v>
+        <v>5100347225</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J55" s="1">
         <v>0</v>
       </c>
       <c r="K55" s="5">
-        <v>-91703429</v>
+        <v>-5349729</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N55" s="6" t="str">
-        <f t="shared" ref="N55:N56" si="15">+H55&amp;" "&amp; E55</f>
-        <v>Factura Acrededor PMP1276990</v>
-      </c>
-      <c r="O55" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>1730</v>
+        <v>1766</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>16</v>
@@ -3269,43 +3008,35 @@
         <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G56" s="1">
-        <v>5100337687</v>
+        <v>5100347331</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J56" s="1">
         <v>0</v>
       </c>
       <c r="K56" s="5">
-        <v>-357532623</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>28</v>
+        <v>-61576440</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N56" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v>Factura Acrededor PMP1277143</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>1731</v>
+        <v>1767</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>16</v>
@@ -3317,43 +3048,35 @@
         <v>17</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G57" s="1">
-        <v>5100337688</v>
+        <v>5100347332</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
       </c>
       <c r="K57" s="5">
-        <v>18833393</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>28</v>
+        <v>9237918</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N57" s="6" t="str">
-        <f>+H57&amp;" "&amp;E57</f>
-        <v>Reduc Factura Compra PMP1277143</v>
-      </c>
-      <c r="O57" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <v>1732</v>
+        <v>1768</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>16</v>
@@ -3365,43 +3088,38 @@
         <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G58" s="1">
-        <v>5100337954</v>
+        <v>5100347419</v>
       </c>
       <c r="H58" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5">
+        <v>-893760</v>
+      </c>
+      <c r="L58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="5">
-        <v>-334587580</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="M58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N58" s="6" t="str">
-        <f>+H58&amp;" "&amp; E58</f>
-        <v>Factura Acrededor PMP1277142</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>1733</v>
+        <v>1769</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>16</v>
@@ -3413,43 +3131,38 @@
         <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G59" s="1">
-        <v>5100337955</v>
+        <v>5100347532</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J59" s="1">
         <v>0</v>
       </c>
       <c r="K59" s="5">
-        <v>1272672</v>
+        <v>-26535708</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N59" s="6" t="str">
-        <f t="shared" ref="N59:N60" si="16">+H59&amp;" "&amp;E59</f>
-        <v>Reduc Factura Compra PMP1277142</v>
-      </c>
-      <c r="O59" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>1735</v>
+        <v>1770</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>16</v>
@@ -3461,40 +3174,38 @@
         <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G60" s="1">
-        <v>5100337288</v>
+        <v>5100347533</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J60" s="1">
         <v>0</v>
       </c>
       <c r="K60" s="5">
-        <v>182382</v>
+        <v>127908</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N60" s="6" t="str">
-        <f t="shared" si="16"/>
-        <v>Reduc Factura Compra PMP1276988</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>1736</v>
+        <v>1771</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>16</v>
@@ -3506,40 +3217,38 @@
         <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G61" s="1">
-        <v>5100337287</v>
+        <v>5100347535</v>
       </c>
       <c r="H61" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5">
+        <v>-1681732</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J61" s="1">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5">
-        <v>-111183834</v>
-      </c>
       <c r="M61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N61" s="6" t="str">
-        <f>+H61&amp;" "&amp; E61</f>
-        <v>Factura Acrededor PMP1276988</v>
-      </c>
-      <c r="O61" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>1756</v>
+        <v>1772</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>16</v>
@@ -3551,43 +3260,35 @@
         <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G62" s="1">
-        <v>1700027700</v>
+        <v>5100348718</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J62" s="1">
         <v>0</v>
       </c>
       <c r="K62" s="5">
-        <v>6022678</v>
+        <v>-48558526</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N62" s="6" t="str">
-        <f t="shared" ref="N62:N64" si="17">+M62</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>1757</v>
+        <v>1773</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>16</v>
@@ -3599,43 +3300,35 @@
         <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G63" s="1">
-        <v>1700028006</v>
+        <v>5100348719</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J63" s="1">
         <v>0</v>
       </c>
       <c r="K63" s="5">
-        <v>7052198</v>
+        <v>229556</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N63" s="6" t="str">
-        <f t="shared" si="17"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O63" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>1758</v>
+        <v>1774</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>16</v>
@@ -3647,40 +3340,35 @@
         <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G64" s="1">
-        <v>1700028197</v>
+        <v>5100348738</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J64" s="1">
         <v>0</v>
       </c>
       <c r="K64" s="5">
-        <v>22568987</v>
-      </c>
-      <c r="M64" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N64" s="6" t="str">
-        <f t="shared" si="17"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>-105495728</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>1765</v>
+        <v>1775</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>16</v>
@@ -3692,43 +3380,35 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G65" s="1">
-        <v>1700027506</v>
+        <v>5100348739</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J65" s="1">
         <v>0</v>
       </c>
       <c r="K65" s="5">
-        <v>8073343</v>
+        <v>599933</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M65" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N65" s="6" t="str">
-        <f t="shared" ref="N65:N67" si="18">+M65</f>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O65" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>1766</v>
+        <v>1776</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>16</v>
@@ -3740,43 +3420,38 @@
         <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G66" s="1">
-        <v>1700027318</v>
+        <v>5100346890</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J66" s="1">
         <v>0</v>
       </c>
       <c r="K66" s="5">
-        <v>3057002</v>
+        <v>6107713</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N66" s="6" t="str">
-        <f t="shared" si="18"/>
-        <v>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>16</v>
@@ -3788,16 +3463,16 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G67" s="1">
-        <v>1700028337</v>
+        <v>5100346889</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>31</v>
@@ -3806,36 +3481,598 @@
         <v>0</v>
       </c>
       <c r="K67" s="5">
-        <v>481837</v>
+        <v>-40711695</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N67" s="6" t="str">
-        <f t="shared" si="18"/>
-        <v>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</v>
-      </c>
-      <c r="O67" s="6" t="s">
-        <v>50</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>1778</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" s="1">
+        <v>5100346865</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
       <c r="K68" s="5">
-        <f>SUBTOTAL(9,K3:K67)</f>
-        <v>-1017083580</v>
+        <v>-7636175</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N68" s="6">
-        <f t="shared" ref="N68" si="19">+M68</f>
+        <f t="shared" ref="N68" si="0">+M68</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>1779</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G69" s="1">
+        <v>5100346803</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
       <c r="K69" s="5">
-        <f>+K68*2%</f>
-        <v>-20341671.600000001</v>
+        <v>5263</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>1780</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" s="1">
+        <v>5100346802</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5">
+        <v>-68750061</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>1781</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71" s="1">
+        <v>5100346776</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="5">
+        <v>-232560</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>1782</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G72" s="1">
+        <v>5100346718</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="5">
+        <v>-2010960</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>1783</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G73" s="1">
+        <v>5100346774</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" s="5">
+        <v>-25633941</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>1828</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="1">
+        <v>5009127718</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G74" s="1">
+        <v>5100363412</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="5">
+        <v>8284</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>1829</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="1">
+        <v>5009127697</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G75" s="1">
+        <v>5100363396</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="5">
+        <v>84813</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>1831</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="1">
+        <v>5009135265</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G76" s="1">
+        <v>5100365247</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="5">
+        <v>19380</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>1832</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="1">
+        <v>5009132652</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G77" s="1">
+        <v>5100364503</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J77" s="1">
+        <v>0</v>
+      </c>
+      <c r="K77" s="5">
+        <v>1537986</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>1833</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="1">
+        <v>5009128791</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G78" s="1">
+        <v>5100363866</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" s="5">
+        <v>297613</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>1834</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="1">
+        <v>5009141130</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G79" s="1">
+        <v>5100366672</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="5">
+        <v>21203</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>1835</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="1">
+        <v>5009142444</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G80" s="1">
+        <v>5100367090</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J80" s="1">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5">
+        <v>154539</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>1837</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="5">
+        <v>-961634932</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>1838</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J82" s="1">
+        <v>0</v>
+      </c>
+      <c r="K82" s="5">
+        <v>961634932</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/app/Archivos/Remittance/Remittance_copi.xlsx
+++ b/app/Archivos/Remittance/Remittance_copi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unilever-my.sharepoint.com/personal/jose-ricardo_morales_unilever_com/Documents/Cartera/PROYECTOS/Cash App Cross Andina/Python/Unilever_Collect_Digital/app/Archivos/Remittance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{44AC9C51-96AC-4375-9CE1-1101779D2EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{105E4711-CDDC-4FBF-919A-7542182BA466}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{44AC9C51-96AC-4375-9CE1-1101779D2EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB6AC2B8-D709-400F-B7C4-9005A75D20A7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A4FF0199-2636-4D5A-A5AA-72A4E1DC7BA9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="99">
   <si>
     <t>Facturas Pagadas
 Proveedor: UNILEVER ANDINA COLOMBIA LTDA
@@ -121,85 +121,223 @@
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>UNILEVER ANDINA COLOMBIA LTDA // CONCILIACIÓN</t>
-  </si>
-  <si>
-    <t>Traslado Notas  Deudor acreedor</t>
-  </si>
-  <si>
-    <t>PMP1280917</t>
-  </si>
-  <si>
-    <t>24/09/2025</t>
-  </si>
-  <si>
-    <t>27/08/2025</t>
-  </si>
-  <si>
-    <t>PMP1280912</t>
-  </si>
-  <si>
-    <t>PMP1282411</t>
-  </si>
-  <si>
-    <t>03/09/2025</t>
-  </si>
-  <si>
-    <t>PMP1282416</t>
-  </si>
-  <si>
-    <t>ACT COMERCIAL</t>
-  </si>
-  <si>
-    <t>FCR MEGSEM COT 10-30 AGO 2025</t>
-  </si>
-  <si>
-    <t>FCR MEGSEM COT 4-30 AGO 2025 A</t>
-  </si>
-  <si>
-    <t>TRASLADO DEUDOR</t>
-  </si>
-  <si>
-    <t>0107848931</t>
-  </si>
-  <si>
-    <t>TD 36164908-36164969-36164976</t>
-  </si>
-  <si>
-    <t>FCR MEG SEM PAIS 10-30 AGO 2025 CPS</t>
-  </si>
-  <si>
-    <t>PMP1280914</t>
-  </si>
-  <si>
-    <t>PMP1282415</t>
-  </si>
-  <si>
-    <t>PMP1282409</t>
-  </si>
-  <si>
-    <t>PMP1282410</t>
-  </si>
-  <si>
-    <t>PMP1280915</t>
-  </si>
-  <si>
-    <t>PMP1282417</t>
-  </si>
-  <si>
-    <t>PMP1282412</t>
-  </si>
-  <si>
-    <t>PMP1280918</t>
-  </si>
-  <si>
-    <t>PMP1282407</t>
-  </si>
-  <si>
-    <t>PMP1282408</t>
+    <t>PMP1268874</t>
+  </si>
+  <si>
+    <t>26/09/2025</t>
+  </si>
+  <si>
+    <t>29/07/2025</t>
+  </si>
+  <si>
+    <t>PMP1282661</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
+    <t>Cerritos</t>
+  </si>
+  <si>
+    <t>PMP1282667</t>
+  </si>
+  <si>
+    <t>PMP1281981</t>
+  </si>
+  <si>
+    <t>02/09/2025</t>
+  </si>
+  <si>
+    <t>PMP1281985</t>
+  </si>
+  <si>
+    <t>PMP1282976</t>
+  </si>
+  <si>
+    <t>04/09/2025</t>
+  </si>
+  <si>
+    <t>Bucaramanga ZF</t>
+  </si>
+  <si>
+    <t>PMP1282969</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA COLOMBINA LIMITADA/CONCILIACION</t>
+  </si>
+  <si>
+    <t>PMP1266923</t>
+  </si>
+  <si>
+    <t>21/07/2025</t>
+  </si>
+  <si>
+    <t>PMP1266922</t>
+  </si>
+  <si>
+    <t>22/07/2025</t>
+  </si>
+  <si>
+    <t>PMP1268211</t>
+  </si>
+  <si>
+    <t>27/07/2025</t>
+  </si>
+  <si>
+    <t>Palmira</t>
+  </si>
+  <si>
+    <t>PMP1266733</t>
+  </si>
+  <si>
+    <t>24/07/2025</t>
+  </si>
+  <si>
+    <t>PMP1266731</t>
+  </si>
+  <si>
+    <t>PMP1268214</t>
+  </si>
+  <si>
+    <t>PMP1268170</t>
+  </si>
+  <si>
+    <t>PMP1267820</t>
+  </si>
+  <si>
+    <t>26/07/2025</t>
+  </si>
+  <si>
+    <t>PMP1267822</t>
+  </si>
+  <si>
+    <t>PMP1281979</t>
+  </si>
+  <si>
+    <t>PMP1281983</t>
+  </si>
+  <si>
+    <t>PMP1282664</t>
+  </si>
+  <si>
+    <t>PMP1282665</t>
+  </si>
+  <si>
+    <t>PMP1282977</t>
+  </si>
+  <si>
+    <t>PMP1282967</t>
+  </si>
+  <si>
+    <t>PMP1282971</t>
+  </si>
+  <si>
+    <t>PMP1266732</t>
+  </si>
+  <si>
+    <t>PMP1268212</t>
+  </si>
+  <si>
+    <t>PMP1266925</t>
+  </si>
+  <si>
+    <t>PMP1268168</t>
+  </si>
+  <si>
+    <t>UNILEVER ANDINA COLOMBIA LTDA/ONCILIACION</t>
+  </si>
+  <si>
+    <t>PMP1267821</t>
+  </si>
+  <si>
+    <t>PMP1276957</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>PMP1277188</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>PMP1279351</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>PMP1266924</t>
+  </si>
+  <si>
+    <t>PMP1268213</t>
+  </si>
+  <si>
+    <t>PMP1266734</t>
+  </si>
+  <si>
+    <t>PMP1267823</t>
+  </si>
+  <si>
+    <t>PMP1268169</t>
+  </si>
+  <si>
+    <t>UNILEVER ANDINA COLOMBIA LTDA/CONCILÑIACION</t>
+  </si>
+  <si>
+    <t>PMP1282666</t>
+  </si>
+  <si>
+    <t>PMP1281984</t>
+  </si>
+  <si>
+    <t>PMP1282669</t>
+  </si>
+  <si>
+    <t>PMP1281977</t>
+  </si>
+  <si>
+    <t>PMP1282966</t>
+  </si>
+  <si>
+    <t>PMP1282973</t>
+  </si>
+  <si>
+    <t>Devolucion</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>PMP-1276956</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>PMP1279348</t>
+  </si>
+  <si>
+    <t>UNILEVER ANDINA COLOMBIA LTD/conciliacion</t>
+  </si>
+  <si>
+    <t>PMP1281980</t>
+  </si>
+  <si>
+    <t>PMP1282663</t>
+  </si>
+  <si>
+    <t>PMP1281982</t>
+  </si>
+  <si>
+    <t>PMP1282668</t>
+  </si>
+  <si>
+    <t>PMP1282968</t>
+  </si>
+  <si>
+    <t>PMP1282970</t>
   </si>
 </sst>
 </file>
@@ -643,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA5F87B-7EBD-4E78-9BF0-7A754A9939D9}">
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -731,7 +869,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>331</v>
+        <v>196</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -743,38 +881,35 @@
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1">
-        <v>5100351507</v>
+        <v>5100294518</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>5070589</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>25</v>
+        <v>8432979</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>332</v>
+        <v>198</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>16</v>
@@ -786,38 +921,35 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G4" s="1">
-        <v>5100351500</v>
+        <v>5100294517</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>-956619</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>25</v>
+        <v>-21081686</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -832,35 +964,32 @@
         <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1">
-        <v>5100351506</v>
+        <v>5100354515</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>-4275345</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>-12675696</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
@@ -872,38 +1001,35 @@
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5100354501</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="1">
-        <v>5100352639</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>-38780386</v>
+        <v>2401857</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>16</v>
@@ -918,10 +1044,10 @@
         <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G7" s="1">
-        <v>5100352640</v>
+        <v>5100354076</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>18</v>
@@ -933,20 +1059,17 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>884601</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>21</v>
+        <v>115382</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
@@ -961,13 +1084,13 @@
         <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1">
-        <v>5100352892</v>
+        <v>5100354251</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>34</v>
@@ -976,10 +1099,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>-50836218</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>21</v>
+        <v>4536842</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>19</v>
@@ -989,7 +1109,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>16</v>
@@ -1001,38 +1121,35 @@
         <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5100354500</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="1">
-        <v>5100352893</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>20335730</v>
+        <v>-6004277</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>16</v>
@@ -1044,38 +1161,35 @@
         <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G10" s="1">
-        <v>1700029668</v>
+        <v>5100354250</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>24396053</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>21</v>
+        <v>-11341412</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>16</v>
@@ -1087,38 +1201,35 @@
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1">
-        <v>1700029712</v>
+        <v>5100354075</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>25500117</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>21</v>
+        <v>-12168111</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>16</v>
@@ -1130,38 +1241,38 @@
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5100356895</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>8565708</v>
+        <v>-2134854</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
@@ -1173,35 +1284,38 @@
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1">
-        <v>1700029790</v>
+        <v>5100356896</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>7432616</v>
+        <v>853994</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>16</v>
@@ -1212,36 +1326,39 @@
       <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1">
-        <v>1700029785</v>
+        <v>5100357661</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14" s="5">
-        <v>52403602</v>
+        <v>38461</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>638</v>
+        <v>360</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -1253,38 +1370,38 @@
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1">
-        <v>5100351467</v>
+        <v>5100357660</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>-6664808</v>
+        <v>-5248033</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>639</v>
+        <v>394</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
@@ -1296,38 +1413,35 @@
         <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G16" s="1">
-        <v>5100351468</v>
+        <v>1700029969</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>2354256</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>25</v>
+        <v>4710714</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>641</v>
+        <v>526</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
@@ -1339,38 +1453,38 @@
         <v>17</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G17" s="1">
-        <v>5100352619</v>
+        <v>5100291666</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>-68978368</v>
+        <v>-27825806</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>642</v>
+        <v>527</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
@@ -1382,38 +1496,38 @@
         <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G18" s="1">
-        <v>5100352631</v>
+        <v>5100291667</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
       </c>
       <c r="K18" s="5">
-        <v>581114</v>
+        <v>8347760</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>643</v>
+        <v>528</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -1425,38 +1539,38 @@
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" s="1">
-        <v>5100352620</v>
+        <v>5100291633</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>24143415</v>
+        <v>4227893</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>644</v>
+        <v>529</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>16</v>
@@ -1468,38 +1582,38 @@
         <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" s="1">
-        <v>5100352630</v>
+        <v>5100291632</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="5">
-        <v>-47933755</v>
+        <v>-14091996</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>652</v>
+        <v>530</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>16</v>
@@ -1511,28 +1625,28 @@
         <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="1">
+        <v>5100291311</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="1">
-        <v>5100352941</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="J21" s="1">
         <v>0</v>
       </c>
       <c r="K21" s="5">
-        <v>-900649</v>
+        <v>10052530</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>17</v>
@@ -1542,7 +1656,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>1353</v>
+        <v>531</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
@@ -1554,28 +1668,28 @@
         <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="1">
+        <v>5100291310</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>-33507174</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="1">
-        <v>5100351499</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5">
-        <v>1161934</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>17</v>
@@ -1585,7 +1699,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>1355</v>
+        <v>532</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -1597,38 +1711,35 @@
         <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G23" s="1">
-        <v>5100351498</v>
+        <v>5100291220</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="J23" s="1">
         <v>0</v>
       </c>
       <c r="K23" s="5">
-        <v>-2904807</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>25</v>
+        <v>11015386</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>1359</v>
+        <v>533</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>16</v>
@@ -1640,28 +1751,25 @@
         <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G24" s="1">
-        <v>5100352872</v>
+        <v>5100291230</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="J24" s="1">
         <v>0</v>
       </c>
       <c r="K24" s="5">
-        <v>922315</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>21</v>
+        <v>-18789070</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>19</v>
@@ -1671,7 +1779,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>1360</v>
+        <v>534</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>16</v>
@@ -1686,25 +1794,22 @@
         <v>48</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G25" s="1">
-        <v>5100352871</v>
+        <v>5100291219</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="J25" s="1">
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>-67654945</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>21</v>
+        <v>-36720021</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>19</v>
@@ -1714,7 +1819,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>1362</v>
+        <v>536</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>16</v>
@@ -1726,38 +1831,38 @@
         <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G26" s="1">
-        <v>5100352607</v>
+        <v>5100291268</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J26" s="1">
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <v>49382170</v>
+        <v>18062497</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>1370</v>
+        <v>539</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>16</v>
@@ -1769,38 +1874,38 @@
         <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G27" s="1">
-        <v>5100352606</v>
+        <v>5100291267</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J27" s="1">
         <v>0</v>
       </c>
       <c r="K27" s="5">
-        <v>-123454295</v>
+        <v>-60211711</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>1797</v>
+        <v>540</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>16</v>
@@ -1815,35 +1920,32 @@
         <v>50</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G28" s="1">
-        <v>5100351487</v>
+        <v>5100291231</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="J28" s="1">
         <v>0</v>
       </c>
       <c r="K28" s="5">
-        <v>-33587149</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>25</v>
+        <v>5636932</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>1800</v>
+        <v>543</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>16</v>
@@ -1855,38 +1957,38 @@
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G29" s="1">
-        <v>5100351488</v>
+        <v>5100292877</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
       </c>
       <c r="K29" s="5">
-        <v>5038863</v>
+        <v>58839957</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>1801</v>
+        <v>544</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>16</v>
@@ -1898,38 +2000,35 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G30" s="1">
-        <v>5100352895</v>
+        <v>5100293401</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J30" s="1">
         <v>0</v>
       </c>
       <c r="K30" s="5">
-        <v>-75473016</v>
+        <v>-20667976</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>1802</v>
+        <v>545</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>16</v>
@@ -1941,38 +2040,35 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G31" s="1">
-        <v>5100352896</v>
+        <v>5100293402</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J31" s="1">
         <v>0</v>
       </c>
       <c r="K31" s="5">
-        <v>1359799</v>
+        <v>6200625</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>1803</v>
+        <v>546</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>16</v>
@@ -1984,38 +2080,35 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G32" s="1">
-        <v>5100352922</v>
+        <v>5100293407</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J32" s="1">
         <v>0</v>
       </c>
       <c r="K32" s="5">
-        <v>-23442473</v>
+        <v>-34895424</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>1804</v>
+        <v>547</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>16</v>
@@ -2030,22 +2123,22 @@
         <v>52</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G33" s="1">
-        <v>5100352923</v>
+        <v>5100292876</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J33" s="1">
         <v>0</v>
       </c>
       <c r="K33" s="5">
-        <v>767748</v>
+        <v>-196144213</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>21</v>
@@ -2057,143 +2150,2668 @@
       <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>548</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="1">
+        <v>5100293408</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5">
+        <v>10468041</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>684</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5100353995</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5">
+        <v>111133</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>685</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" s="1">
+        <v>5100353994</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
+        <v>-8329474</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>686</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5100353952</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>6727283</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>687</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" s="1">
+        <v>5100354517</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <v>-3296919</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>688</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" s="1">
+        <v>5100353951</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <v>-20363185</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N39" s="6"/>
       <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>689</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G40" s="1">
+        <v>5100354445</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
+        <v>2493239</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>690</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5100354444</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5">
+        <v>-7477794</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>692</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G42" s="1">
+        <v>5100356921</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5">
+        <v>1133530</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>693</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G43" s="1">
+        <v>5100356920</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5">
+        <v>-3208982</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>694</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" s="1">
+        <v>5100356867</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5">
+        <v>-285000</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>696</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G45" s="1">
+        <v>5100357762</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="5">
+        <v>96296</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>697</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" s="1">
+        <v>5100357761</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5">
+        <v>-4328147</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>889</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="1">
+        <v>5100290792</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
+        <v>5730027</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N47" s="6"/>
       <c r="O47" s="6"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>890</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G48" s="1">
+        <v>5100290791</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5">
+        <v>-14325031</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
     </row>
-    <row r="49" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>891</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G49" s="1">
+        <v>5100291295</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="5">
+        <v>16520236</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
     </row>
-    <row r="50" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>892</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" s="1">
+        <v>5100291708</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5">
+        <v>-14138774</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
     </row>
-    <row r="51" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>895</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" s="1">
+        <v>5100291709</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="5">
+        <v>5655358</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
     </row>
-    <row r="52" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>903</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" s="1">
+        <v>5100291294</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5">
+        <v>-41300741</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
     </row>
-    <row r="53" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>907</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5100292893</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="5">
+        <v>-110693428</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
     </row>
-    <row r="54" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>908</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="1">
+        <v>5100292894</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5">
+        <v>44277142</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
     </row>
-    <row r="55" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>912</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" s="1">
+        <v>5100293382</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5">
+        <v>9153161</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="N55" s="6"/>
       <c r="O55" s="6"/>
     </row>
-    <row r="56" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>913</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="1">
+        <v>5100293381</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5">
+        <v>-22882843</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="N56" s="6"/>
       <c r="O56" s="6"/>
     </row>
-    <row r="57" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>1013</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="1">
+        <v>5100339662</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5">
+        <v>-3334618</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N57" s="6"/>
       <c r="O57" s="6"/>
     </row>
-    <row r="58" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>1016</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" s="1">
+        <v>5100339663</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5">
+        <v>313646</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
     </row>
-    <row r="59" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>1018</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" s="1">
+        <v>5100342120</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="5">
+        <v>10758</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N59" s="6"/>
       <c r="O59" s="6"/>
     </row>
-    <row r="60" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>1020</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" s="1">
+        <v>5100342119</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5">
+        <v>-4409576</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N60" s="6"/>
       <c r="O60" s="6"/>
     </row>
-    <row r="61" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>1021</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="1">
+        <v>5100342454</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5">
+        <v>-61045242</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
     </row>
-    <row r="62" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>1022</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G62" s="1">
+        <v>5100342455</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5">
+        <v>719015</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N62" s="6"/>
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1264</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5100291693</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" s="5">
+        <v>12084101</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N63" s="6"/>
       <c r="O63" s="6"/>
     </row>
-    <row r="64" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>1265</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="1">
+        <v>5100291692</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="5">
+        <v>-30210288</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N64" s="6"/>
       <c r="O64" s="6"/>
     </row>
-    <row r="65" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>1266</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="1">
+        <v>5100291330</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="5">
+        <v>26956181</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N65" s="6"/>
       <c r="O65" s="6"/>
     </row>
-    <row r="66" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>1267</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" s="1">
+        <v>5100291329</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5">
+        <v>-67391530</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N66" s="6"/>
       <c r="O66" s="6"/>
     </row>
-    <row r="67" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>1269</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5100291209</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="5">
+        <v>6739044</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N67" s="6"/>
       <c r="O67" s="6"/>
     </row>
-    <row r="68" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>1270</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" s="1">
+        <v>5100291208</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="5">
+        <v>-16847879</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>1272</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" s="1">
+        <v>5100293392</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5">
+        <v>-43572103</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>1273</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G70" s="1">
+        <v>5100293393</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5">
+        <v>17428565</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>1276</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G71" s="1">
+        <v>5100292813</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="5">
+        <v>-259980219</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>1277</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G72" s="1">
+        <v>5100292814</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="5">
+        <v>103990360</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>1420</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G73" s="1">
+        <v>5100354442</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" s="5">
+        <v>-12781158</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>1421</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G74" s="1">
+        <v>5100354196</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="5">
+        <v>31023621</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>1422</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G75" s="1">
+        <v>5100354512</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="5">
+        <v>-2413370</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>1423</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G76" s="1">
+        <v>5100354195</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="5">
+        <v>-77558344</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>1424</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G77" s="1">
+        <v>5100354172</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J77" s="1">
+        <v>0</v>
+      </c>
+      <c r="K77" s="5">
+        <v>544786</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>1425</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G78" s="1">
+        <v>5100354171</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" s="5">
+        <v>-37616335</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>1426</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G79" s="1">
+        <v>5100354443</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="5">
+        <v>5112507</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>1428</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80" s="1">
+        <v>5100357820</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J80" s="1">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5">
+        <v>-12364011</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>1429</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G81" s="1">
+        <v>5100357821</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="5">
+        <v>488651</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>1431</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G82" s="1">
+        <v>5100357652</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J82" s="1">
+        <v>0</v>
+      </c>
+      <c r="K82" s="5">
+        <v>5925860</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>1432</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G83" s="1">
+        <v>5100357651</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J83" s="1">
+        <v>0</v>
+      </c>
+      <c r="K83" s="5">
+        <v>-14814515</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>1450</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="1">
+        <v>5009169652</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G84" s="1">
+        <v>5100374214</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J84" s="1">
+        <v>0</v>
+      </c>
+      <c r="K84" s="5">
+        <v>17472</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>1801</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G85" s="1">
+        <v>5100340001</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J85" s="1">
+        <v>0</v>
+      </c>
+      <c r="K85" s="5">
+        <v>859348</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>1812</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G86" s="1">
+        <v>5100340698</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J86" s="1">
+        <v>0</v>
+      </c>
+      <c r="K86" s="5">
+        <v>895</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>1878</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G87" s="1">
+        <v>5100353981</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J87" s="1">
+        <v>0</v>
+      </c>
+      <c r="K87" s="5">
+        <v>276976</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>1879</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G88" s="1">
+        <v>5100353980</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J88" s="1">
+        <v>0</v>
+      </c>
+      <c r="K88" s="5">
+        <v>-14563708</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>1880</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G89" s="1">
+        <v>5100354513</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J89" s="1">
+        <v>0</v>
+      </c>
+      <c r="K89" s="5">
+        <v>-1816693</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>1881</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G90" s="1">
+        <v>5100353909</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J90" s="1">
+        <v>0</v>
+      </c>
+      <c r="K90" s="5">
+        <v>-55383891</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>1882</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G91" s="1">
+        <v>5100354514</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J91" s="1">
+        <v>0</v>
+      </c>
+      <c r="K91" s="5">
+        <v>-4432554</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>1883</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G92" s="1">
+        <v>5100353910</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J92" s="1">
+        <v>0</v>
+      </c>
+      <c r="K92" s="5">
+        <v>851509</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>1886</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G93" s="1">
+        <v>5100357677</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J93" s="1">
+        <v>0</v>
+      </c>
+      <c r="K93" s="5">
+        <v>31780</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>1887</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G94" s="1">
+        <v>5100357768</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J94" s="1">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5">
+        <v>72829</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>1890</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G95" s="1">
+        <v>5100357676</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J95" s="1">
+        <v>0</v>
+      </c>
+      <c r="K95" s="5">
+        <v>-4778339</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>1891</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G96" s="1">
+        <v>5100357767</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J96" s="1">
+        <v>0</v>
+      </c>
+      <c r="K96" s="5">
+        <v>-16139587</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>1919</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="1">
+        <v>5009172203</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G97" s="1">
+        <v>5100374615</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J97" s="1">
+        <v>0</v>
+      </c>
+      <c r="K97" s="5">
+        <v>21203</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>1920</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="1">
+        <v>5009168234</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G98" s="1">
+        <v>5100374016</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J98" s="1">
+        <v>0</v>
+      </c>
+      <c r="K98" s="5">
+        <v>116282</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>1921</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="1">
+        <v>860002518</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="1">
+        <v>5009175094</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G99" s="1">
+        <v>5100375784</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J99" s="1">
+        <v>0</v>
+      </c>
+      <c r="K99" s="5">
+        <v>21203</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:O69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
